--- a/data/trans_orig/P17A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P17A-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consultado con algún médico (público o privado) por agún problema, molestia o enfermedad suya en las últimas dos semanas en 2007</t>
+          <t>Población que ha tenido una consulta médica (pública o privada) por algún problema, molestia o enfermedad suya en las últimas 2 semanas en 2007 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>303762</t>
+          <t>306489</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>363789</t>
+          <t>366613</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>494880</t>
+          <t>495495</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>562895</t>
+          <t>568286</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>814022</t>
+          <t>815310</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>909007</t>
+          <t>906525</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>38,64%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>667000</t>
+          <t>664176</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>727027</t>
+          <t>724300</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>752218</t>
+          <t>746827</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>820233</t>
+          <t>819618</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1436894</t>
+          <t>1439376</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1531879</t>
+          <t>1530591</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>65,25%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>223066</t>
+          <t>221157</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>281374</t>
+          <t>284212</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>371789</t>
+          <t>370575</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>438219</t>
+          <t>439659</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>611610</t>
+          <t>611013</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>703136</t>
+          <t>703675</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1410303</t>
+          <t>1407465</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1468611</t>
+          <t>1470520</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1147442</t>
+          <t>1146002</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1213872</t>
+          <t>1215086</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2574202</t>
+          <t>2573663</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2665728</t>
+          <t>2666325</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>81,36%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55956</t>
+          <t>56787</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>91070</t>
+          <t>90433</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>99502</t>
+          <t>98749</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>137605</t>
+          <t>135621</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>162057</t>
+          <t>164422</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>212515</t>
+          <t>212774</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,7%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>460338</t>
+          <t>460975</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>495452</t>
+          <t>494621</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>338807</t>
+          <t>340791</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>376910</t>
+          <t>377663</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>815305</t>
+          <t>815046</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>865763</t>
+          <t>863398</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,0%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>617762</t>
+          <t>610391</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>705959</t>
+          <t>701611</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>997604</t>
+          <t>989297</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1105986</t>
+          <t>1095103</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1636471</t>
+          <t>1642244</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1788573</t>
+          <t>1780854</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,78%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2567915</t>
+          <t>2572263</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2656112</t>
+          <t>2663483</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2271199</t>
+          <t>2282082</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2379581</t>
+          <t>2387888</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4862486</t>
+          <t>4870205</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5014588</t>
+          <t>5008815</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,31%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consultado con algún médico (público o privado) por agún problema, molestia o enfermedad suya en las últimas dos semanas en 2012</t>
+          <t>Población que ha tenido una consulta médica (pública o privada) por algún problema, molestia o enfermedad suya en las últimas 2 semanas en 2012 (tasa de respuesta: 99,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>312612</t>
+          <t>313421</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>376954</t>
+          <t>371970</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>515616</t>
+          <t>508675</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>586650</t>
+          <t>583692</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>847449</t>
+          <t>848149</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>948988</t>
+          <t>946236</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>40,99%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>595524</t>
+          <t>600508</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>659866</t>
+          <t>659057</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>749133</t>
+          <t>752091</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>820167</t>
+          <t>827108</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1359273</t>
+          <t>1362025</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1460812</t>
+          <t>1460112</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,26%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>319929</t>
+          <t>327532</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>391313</t>
+          <t>396431</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>456394</t>
+          <t>454258</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>535664</t>
+          <t>535763</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>798935</t>
+          <t>805506</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>904821</t>
+          <t>913904</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,66%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1564738</t>
+          <t>1559620</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1636122</t>
+          <t>1628519</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1214031</t>
+          <t>1213932</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1293301</t>
+          <t>1295437</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2800925</t>
+          <t>2791842</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2906811</t>
+          <t>2900240</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,26%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59959</t>
+          <t>58697</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>96338</t>
+          <t>94041</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>90855</t>
+          <t>90185</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>130464</t>
+          <t>131104</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,47 +3072,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>19,7%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>28,65%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>185644</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>158603</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>212814</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
           <t>19,85%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>28,51%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>185644</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>161159</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>215558</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>19,85%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,76%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>380999</t>
+          <t>383296</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>417378</t>
+          <t>418640</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>327217</t>
+          <t>326577</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>366826</t>
+          <t>367496</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,47 +3185,47 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
+          <t>80,3%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>686</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>749374</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>722204</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>776415</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
           <t>80,15%</t>
         </is>
       </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>686</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>749374</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>719460</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>773859</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>80,15%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>83,04%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>725205</t>
+          <t>725521</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>826762</t>
+          <t>827875</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1097762</t>
+          <t>1095530</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1208808</t>
+          <t>1210777</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1856196</t>
+          <t>1854722</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2016515</t>
+          <t>2012832</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,97%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2579104</t>
+          <t>2577991</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2680661</t>
+          <t>2680345</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2334351</t>
+          <t>2332382</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2445397</t>
+          <t>2447629</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4932510</t>
+          <t>4936193</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5092829</t>
+          <t>5094303</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>71,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,31%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consultado con algún médico (público o privado) por agún problema, molestia o enfermedad suya en las últimas dos semanas en 2016</t>
+          <t>Población que ha tenido una consulta médica (pública o privada) por algún problema, molestia o enfermedad suya en las últimas 2 semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>236421</t>
+          <t>233968</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>289264</t>
+          <t>285099</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>392082</t>
+          <t>387781</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>455217</t>
+          <t>452103</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>639438</t>
+          <t>641565</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>723522</t>
+          <t>722780</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,33%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>465083</t>
+          <t>469248</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>517926</t>
+          <t>520379</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>539443</t>
+          <t>542557</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>602578</t>
+          <t>606879</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1025485</t>
+          <t>1026227</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1109569</t>
+          <t>1107442</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>63,32%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>427830</t>
+          <t>433324</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>513383</t>
+          <t>509700</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>555441</t>
+          <t>553639</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>637803</t>
+          <t>641102</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1006560</t>
+          <t>1007968</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1121614</t>
+          <t>1122230</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,61%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1563002</t>
+          <t>1566685</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1648555</t>
+          <t>1643061</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1350497</t>
+          <t>1347198</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1432859</t>
+          <t>1434661</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2943071</t>
+          <t>2942455</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3058125</t>
+          <t>3056717</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>75,2%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>99673</t>
+          <t>102147</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>140370</t>
+          <t>142523</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>117143</t>
+          <t>119505</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>157492</t>
+          <t>160119</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>231178</t>
+          <t>230155</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>288915</t>
+          <t>289554</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,42%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>406516</t>
+          <t>404363</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>447213</t>
+          <t>444739</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>391648</t>
+          <t>389021</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>431997</t>
+          <t>429635</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>807112</t>
+          <t>806473</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>864849</t>
+          <t>865872</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>79,0%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>796149</t>
+          <t>803438</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>898749</t>
+          <t>903820</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1097592</t>
+          <t>1100537</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1215089</t>
+          <t>1215254</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1928624</t>
+          <t>1931334</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2087239</t>
+          <t>2082648</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,14%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2478869</t>
+          <t>2473798</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2581469</t>
+          <t>2574180</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2317011</t>
+          <t>2316846</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2434508</t>
+          <t>2431563</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4822479</t>
+          <t>4827070</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4981094</t>
+          <t>4978384</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>72,05%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consultado con algún médico (público o privado) por agún problema, molestia o enfermedad suya en las últimas dos semanas en 2023</t>
+          <t>Población que ha tenido una consulta médica (pública o privada) por algún problema, molestia o enfermedad suya en las últimas 2 semanas en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>120490</t>
+          <t>122318</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>156937</t>
+          <t>157310</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>218664</t>
+          <t>218047</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>258565</t>
+          <t>259019</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>346658</t>
+          <t>349752</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>404690</t>
+          <t>403465</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,81%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>357380</t>
+          <t>357007</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>393827</t>
+          <t>391999</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>495555</t>
+          <t>495101</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>535456</t>
+          <t>536073</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>863748</t>
+          <t>864973</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>921780</t>
+          <t>918686</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,43%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>269857</t>
+          <t>254846</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>429601</t>
+          <t>429608</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>380738</t>
+          <t>376169</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>656996</t>
+          <t>653176</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>706468</t>
+          <t>721663</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1059410</t>
+          <t>1062593</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,48%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1859909</t>
+          <t>1859902</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2019653</t>
+          <t>2034664</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1578691</t>
+          <t>1582511</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1854949</t>
+          <t>1859518</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3465787</t>
+          <t>3462604</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3818729</t>
+          <t>3803534</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,05%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>113035</t>
+          <t>113209</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>158344</t>
+          <t>158385</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>135837</t>
+          <t>135333</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>172925</t>
+          <t>174460</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>255241</t>
+          <t>261742</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>314262</t>
+          <t>318500</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,37%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>488279</t>
+          <t>488238</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>533588</t>
+          <t>533414</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>487538</t>
+          <t>486003</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>524626</t>
+          <t>525130</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>992824</t>
+          <t>988586</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1051845</t>
+          <t>1045344</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>79,98%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>508869</t>
+          <t>505561</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>711305</t>
+          <t>711678</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>761291</t>
+          <t>756728</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1040747</t>
+          <t>1040989</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1337889</t>
+          <t>1332209</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1719494</t>
+          <t>1701723</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>23,97%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2739146</t>
+          <t>2738773</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2941582</t>
+          <t>2944890</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2609523</t>
+          <t>2609281</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2888979</t>
+          <t>2893542</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5381227</t>
+          <t>5398998</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5762832</t>
+          <t>5768512</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,24%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P17A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P17A-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>306489</t>
+          <t>308870</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>366613</t>
+          <t>367217</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>495495</t>
+          <t>488808</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>568286</t>
+          <t>561215</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>815310</t>
+          <t>810275</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>906525</t>
+          <t>905806</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,61%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>664176</t>
+          <t>663572</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>724300</t>
+          <t>721919</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>70,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>746827</t>
+          <t>753898</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>819618</t>
+          <t>826305</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1439376</t>
+          <t>1440095</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1530591</t>
+          <t>1535626</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>61,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>65,46%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>221157</t>
+          <t>224096</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>284212</t>
+          <t>284039</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>370575</t>
+          <t>368878</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>439659</t>
+          <t>439789</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>611013</t>
+          <t>611594</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>703675</t>
+          <t>703777</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1407465</t>
+          <t>1407638</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1470520</t>
+          <t>1467581</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1146002</t>
+          <t>1145872</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1215086</t>
+          <t>1216783</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2573663</t>
+          <t>2573561</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2666325</t>
+          <t>2665744</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,34%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56787</t>
+          <t>55886</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>90433</t>
+          <t>89622</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>98749</t>
+          <t>96924</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>135621</t>
+          <t>135511</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>164422</t>
+          <t>163627</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>212774</t>
+          <t>214195</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,84%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>460975</t>
+          <t>461786</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>494621</t>
+          <t>495522</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>340791</t>
+          <t>340901</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>377663</t>
+          <t>379488</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>815046</t>
+          <t>813625</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>863398</t>
+          <t>864193</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,08%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>610391</t>
+          <t>615137</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>701611</t>
+          <t>706471</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>989297</t>
+          <t>994968</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1095103</t>
+          <t>1102982</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1642244</t>
+          <t>1635480</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1780854</t>
+          <t>1776710</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,71%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2572263</t>
+          <t>2567403</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2663483</t>
+          <t>2658737</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2282082</t>
+          <t>2274203</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2387888</t>
+          <t>2382217</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4870205</t>
+          <t>4874349</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5008815</t>
+          <t>5015579</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,41%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>313421</t>
+          <t>312861</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>371970</t>
+          <t>377666</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>508675</t>
+          <t>510375</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>583692</t>
+          <t>586869</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>848149</t>
+          <t>840186</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>946236</t>
+          <t>943665</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>40,88%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>600508</t>
+          <t>594812</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>659057</t>
+          <t>659617</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>752091</t>
+          <t>748914</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>827108</t>
+          <t>825408</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1362025</t>
+          <t>1364596</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1460112</t>
+          <t>1468075</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>63,6%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>327532</t>
+          <t>324614</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>396431</t>
+          <t>397251</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>454258</t>
+          <t>457336</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>535763</t>
+          <t>535157</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>805506</t>
+          <t>799661</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>913904</t>
+          <t>902088</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,34%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1559620</t>
+          <t>1558800</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1628519</t>
+          <t>1631437</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1213932</t>
+          <t>1214538</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1295437</t>
+          <t>1292359</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2791842</t>
+          <t>2803658</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2900240</t>
+          <t>2906085</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,42%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>58697</t>
+          <t>59297</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>94041</t>
+          <t>95479</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>90185</t>
+          <t>89540</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>131104</t>
+          <t>128219</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>158603</t>
+          <t>160195</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>212814</t>
+          <t>213039</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,78%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>383296</t>
+          <t>381858</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>418640</t>
+          <t>418040</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>326577</t>
+          <t>329462</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>367496</t>
+          <t>368141</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>722204</t>
+          <t>721979</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>776415</t>
+          <t>774823</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>82,87%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>725521</t>
+          <t>731106</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>827875</t>
+          <t>835169</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1095530</t>
+          <t>1092356</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1210777</t>
+          <t>1212825</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1854722</t>
+          <t>1859341</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2012832</t>
+          <t>2012915</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2577991</t>
+          <t>2570697</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2680345</t>
+          <t>2674760</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2332382</t>
+          <t>2330334</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2447629</t>
+          <t>2450803</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4936193</t>
+          <t>4936110</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5094303</t>
+          <t>5089684</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,24%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>233968</t>
+          <t>236534</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>285099</t>
+          <t>288301</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>387781</t>
+          <t>389831</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>452103</t>
+          <t>453707</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>641565</t>
+          <t>641236</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>722780</t>
+          <t>724709</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,44%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>469248</t>
+          <t>466046</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>520379</t>
+          <t>517813</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>542557</t>
+          <t>540953</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>606879</t>
+          <t>604829</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1026227</t>
+          <t>1024298</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1107442</t>
+          <t>1107771</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>63,34%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>433324</t>
+          <t>427079</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>509700</t>
+          <t>507845</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>553639</t>
+          <t>556598</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>641102</t>
+          <t>638516</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1007968</t>
+          <t>1003471</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1122230</t>
+          <t>1123007</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,63%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1566685</t>
+          <t>1568540</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1643061</t>
+          <t>1649306</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1347198</t>
+          <t>1349784</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1434661</t>
+          <t>1431702</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2942455</t>
+          <t>2941678</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3056717</t>
+          <t>3061214</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,31%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>102147</t>
+          <t>102041</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>142523</t>
+          <t>144496</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>119505</t>
+          <t>118395</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>160119</t>
+          <t>159243</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>230155</t>
+          <t>228691</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>289554</t>
+          <t>289410</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,41%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>404363</t>
+          <t>402390</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>444739</t>
+          <t>444845</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>73,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>389021</t>
+          <t>389897</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>429635</t>
+          <t>430745</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>806473</t>
+          <t>806617</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>865872</t>
+          <t>867336</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>79,13%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>803438</t>
+          <t>800128</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>903820</t>
+          <t>897496</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1100537</t>
+          <t>1099194</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1215254</t>
+          <t>1213085</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1931334</t>
+          <t>1933405</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2082648</t>
+          <t>2083815</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,16%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2473798</t>
+          <t>2480122</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2574180</t>
+          <t>2577490</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2316846</t>
+          <t>2319015</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2431563</t>
+          <t>2432906</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>65,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4827070</t>
+          <t>4825903</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4978384</t>
+          <t>4976313</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>69,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>72,02%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>137511</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>122318</t>
+          <t>127123</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>157310</t>
+          <t>167091</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>237602</t>
+          <t>257315</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>218047</t>
+          <t>239698</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>259019</t>
+          <t>278576</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>375114</t>
+          <t>404455</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>349752</t>
+          <t>377546</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>403465</t>
+          <t>433213</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>30,98%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>376806</t>
+          <t>430721</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>357007</t>
+          <t>410770</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>391999</t>
+          <t>450738</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>516518</t>
+          <t>563315</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>495101</t>
+          <t>542054</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>536073</t>
+          <t>580932</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>893324</t>
+          <t>994036</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>864973</t>
+          <t>965278</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>918686</t>
+          <t>1020945</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>73,0%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514317</t>
+          <t>577861</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514317</t>
+          <t>577861</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514317</t>
+          <t>577861</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>754120</t>
+          <t>820630</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>754120</t>
+          <t>820630</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>754120</t>
+          <t>820630</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1268438</t>
+          <t>1398491</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1268438</t>
+          <t>1398491</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1268438</t>
+          <t>1398491</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>369658</t>
+          <t>396232</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>254846</t>
+          <t>350933</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>429608</t>
+          <t>432535</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>502340</t>
+          <t>489526</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>376169</t>
+          <t>453120</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>653176</t>
+          <t>526106</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>871998</t>
+          <t>885759</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>721663</t>
+          <t>831687</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1062593</t>
+          <t>938256</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>21,33%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1919852</t>
+          <t>1833429</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1859902</t>
+          <t>1797126</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2034664</t>
+          <t>1878728</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1733347</t>
+          <t>1678649</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1582511</t>
+          <t>1642069</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1859518</t>
+          <t>1715055</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3653199</t>
+          <t>3512077</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3462604</t>
+          <t>3459580</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3803534</t>
+          <t>3566149</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>81,09%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2289510</t>
+          <t>2229661</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2289510</t>
+          <t>2229661</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2289510</t>
+          <t>2229661</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2235687</t>
+          <t>2168175</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2235687</t>
+          <t>2168175</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2235687</t>
+          <t>2168175</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4525197</t>
+          <t>4397836</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4525197</t>
+          <t>4397836</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4525197</t>
+          <t>4397836</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>133483</t>
+          <t>146384</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>113209</t>
+          <t>123279</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>158385</t>
+          <t>170929</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>153456</t>
+          <t>175952</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>135333</t>
+          <t>156007</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>174460</t>
+          <t>198166</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>286939</t>
+          <t>322337</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>261742</t>
+          <t>291117</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>318500</t>
+          <t>357858</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,74%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>513140</t>
+          <t>565203</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>488238</t>
+          <t>540658</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>533414</t>
+          <t>588308</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>507007</t>
+          <t>558925</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>486003</t>
+          <t>536711</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>525130</t>
+          <t>578870</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1020147</t>
+          <t>1124127</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>988586</t>
+          <t>1088606</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1045344</t>
+          <t>1155347</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>79,87%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>640653</t>
+          <t>689757</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>505561</t>
+          <t>637711</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>711678</t>
+          <t>737746</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>893399</t>
+          <t>922793</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>756728</t>
+          <t>869286</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1040989</t>
+          <t>966749</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1534051</t>
+          <t>1612550</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1332209</t>
+          <t>1545917</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1701723</t>
+          <t>1682517</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,23%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2809798</t>
+          <t>2829352</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2738773</t>
+          <t>2781363</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2944890</t>
+          <t>2881398</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2756871</t>
+          <t>2800889</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2609281</t>
+          <t>2756933</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2893542</t>
+          <t>2854396</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5566670</t>
+          <t>5630241</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5398998</t>
+          <t>5560274</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5768512</t>
+          <t>5696874</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>78,66%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3450451</t>
+          <t>3519109</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3450451</t>
+          <t>3519109</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3450451</t>
+          <t>3519109</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3650270</t>
+          <t>3723682</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3650270</t>
+          <t>3723682</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3650270</t>
+          <t>3723682</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7100721</t>
+          <t>7242791</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7100721</t>
+          <t>7242791</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7100721</t>
+          <t>7242791</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
